--- a/data/trans_orig/P36BPD05_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD05_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de carnes rojas, hamburguesas, salchichas o embutidos que consume al día en 2023</t>
+          <t>Población según el número de raciones de carnes rojas, hamburguesas, salchichas o embutidos que consume al día en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109414</t>
+          <t>110064</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>151520</t>
+          <t>149511</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76210</t>
+          <t>77391</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106007</t>
+          <t>105958</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>197640</t>
+          <t>198629</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>246517</t>
+          <t>249124</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>353692</t>
+          <t>355701</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>395798</t>
+          <t>395148</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>340859</t>
+          <t>340908</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>370656</t>
+          <t>369475</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>705561</t>
+          <t>702954</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>754438</t>
+          <t>753449</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,14%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103533</t>
+          <t>103641</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>140482</t>
+          <t>144046</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>81988</t>
+          <t>79953</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110330</t>
+          <t>110082</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>192496</t>
+          <t>193348</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>243845</t>
+          <t>241622</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,03%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311178</t>
+          <t>307614</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>348127</t>
+          <t>348019</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>270226</t>
+          <t>270474</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>298568</t>
+          <t>300603</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>588371</t>
+          <t>590594</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>639720</t>
+          <t>638868</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,77%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>214460</t>
+          <t>214276</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>563223</t>
+          <t>552201</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34239</t>
+          <t>33812</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53127</t>
+          <t>53033</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>252554</t>
+          <t>249390</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>662705</t>
+          <t>673507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>81,01%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>101845</t>
+          <t>112867</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>450608</t>
+          <t>450792</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113218</t>
+          <t>113312</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132106</t>
+          <t>132533</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168708</t>
+          <t>157906</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>578859</t>
+          <t>582023</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>70,0%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>326675</t>
+          <t>328678</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>399516</t>
+          <t>399987</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>260985</t>
+          <t>260722</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>681019</t>
+          <t>695723</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>628308</t>
+          <t>624401</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1144246</t>
+          <t>1150517</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,23%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>635303</t>
+          <t>634832</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>708144</t>
+          <t>706141</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>294426</t>
+          <t>279722</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>714460</t>
+          <t>714723</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>866017</t>
+          <t>859746</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1381955</t>
+          <t>1385862</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,94%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>149526</t>
+          <t>148955</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>198864</t>
+          <t>193315</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>230479</t>
+          <t>227591</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>439033</t>
+          <t>439803</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>399349</t>
+          <t>399937</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>613315</t>
+          <t>607122</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,29%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>272732</t>
+          <t>278281</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>322070</t>
+          <t>322641</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>400977</t>
+          <t>400207</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>609531</t>
+          <t>612419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>698291</t>
+          <t>704484</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>912257</t>
+          <t>911669</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54893</t>
+          <t>54318</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>102248</t>
+          <t>102764</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>210852</t>
+          <t>212372</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>259406</t>
+          <t>261528</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>280590</t>
+          <t>276052</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>347146</t>
+          <t>344509</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>138259</t>
+          <t>137743</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>185614</t>
+          <t>186189</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>500526</t>
+          <t>498404</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>549080</t>
+          <t>547560</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>653293</t>
+          <t>655930</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>719849</t>
+          <t>724387</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,41%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1064105</t>
+          <t>1055369</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1744097</t>
+          <t>1752406</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>985519</t>
+          <t>986957</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1656887</t>
+          <t>1615765</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2109159</t>
+          <t>2112910</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3008918</t>
+          <t>2986882</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,05%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1624766</t>
+          <t>1616457</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2304758</t>
+          <t>2313494</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1912266</t>
+          <t>1953388</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2583634</t>
+          <t>2582196</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3929098</t>
+          <t>3951134</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4828857</t>
+          <t>4825106</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD05_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD05_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>131201</t>
+          <t>144697</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>110064</t>
+          <t>121994</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>149511</t>
+          <t>165928</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>90508</t>
+          <t>98208</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77391</t>
+          <t>83434</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>105958</t>
+          <t>115891</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>221708</t>
+          <t>242905</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>198629</t>
+          <t>217073</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>249124</t>
+          <t>271674</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>374011</t>
+          <t>405921</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>355701</t>
+          <t>384690</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>395148</t>
+          <t>428624</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>356358</t>
+          <t>389590</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>340908</t>
+          <t>371907</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>369475</t>
+          <t>404364</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>730370</t>
+          <t>795511</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>702954</t>
+          <t>766742</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>753449</t>
+          <t>821343</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,1%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446866</t>
+          <t>487798</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446866</t>
+          <t>487798</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446866</t>
+          <t>487798</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952078</t>
+          <t>1038416</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952078</t>
+          <t>1038416</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952078</t>
+          <t>1038416</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>121344</t>
+          <t>132740</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103641</t>
+          <t>113475</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144046</t>
+          <t>153477</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>95214</t>
+          <t>104654</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79953</t>
+          <t>89709</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110082</t>
+          <t>120704</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>216558</t>
+          <t>237394</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>193348</t>
+          <t>210095</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>241622</t>
+          <t>262855</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>330316</t>
+          <t>349796</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>307614</t>
+          <t>329059</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>348019</t>
+          <t>369061</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>285342</t>
+          <t>316429</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>270474</t>
+          <t>300379</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>300603</t>
+          <t>331374</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>615658</t>
+          <t>666225</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>590594</t>
+          <t>640764</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>638868</t>
+          <t>693524</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,75%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451660</t>
+          <t>482536</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451660</t>
+          <t>482536</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451660</t>
+          <t>482536</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>380556</t>
+          <t>421083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>380556</t>
+          <t>421083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>380556</t>
+          <t>421083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>832216</t>
+          <t>903619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>832216</t>
+          <t>903619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>832216</t>
+          <t>903619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>385124</t>
+          <t>157402</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>214276</t>
+          <t>135862</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>552201</t>
+          <t>179514</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42793</t>
+          <t>48227</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33812</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53033</t>
+          <t>59635</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>427917</t>
+          <t>205629</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>249390</t>
+          <t>181623</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>673507</t>
+          <t>230676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>279944</t>
+          <t>310950</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>112867</t>
+          <t>288838</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>450792</t>
+          <t>332490</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>123552</t>
+          <t>138702</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113312</t>
+          <t>127294</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132533</t>
+          <t>148312</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>403496</t>
+          <t>449651</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>157906</t>
+          <t>424604</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>582023</t>
+          <t>473657</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>72,28%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>665068</t>
+          <t>468352</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>665068</t>
+          <t>468352</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>665068</t>
+          <t>468352</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>831413</t>
+          <t>655280</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>831413</t>
+          <t>655280</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>831413</t>
+          <t>655280</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>362702</t>
+          <t>398673</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>328678</t>
+          <t>368209</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>436374</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>417678</t>
+          <t>243493</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>260722</t>
+          <t>221693</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>695723</t>
+          <t>268437</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>780380</t>
+          <t>642166</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>624401</t>
+          <t>597724</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1150517</t>
+          <t>682299</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>34,28%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>672117</t>
+          <t>733170</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>634832</t>
+          <t>695469</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>706141</t>
+          <t>763634</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>557767</t>
+          <t>614932</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>279722</t>
+          <t>589988</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>714723</t>
+          <t>636732</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1229883</t>
+          <t>1348102</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>859746</t>
+          <t>1307969</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1385862</t>
+          <t>1392544</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,97%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>975445</t>
+          <t>858425</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>975445</t>
+          <t>858425</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>975445</t>
+          <t>858425</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2010263</t>
+          <t>1990268</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2010263</t>
+          <t>1990268</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2010263</t>
+          <t>1990268</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>171213</t>
+          <t>198874</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148955</t>
+          <t>172562</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>193315</t>
+          <t>222063</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>290145</t>
+          <t>249553</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>227591</t>
+          <t>227217</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>439803</t>
+          <t>272971</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>461358</t>
+          <t>448427</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>399937</t>
+          <t>412435</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>607122</t>
+          <t>485124</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>34,82%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>300383</t>
+          <t>365493</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>278281</t>
+          <t>342304</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>322641</t>
+          <t>391805</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>549865</t>
+          <t>579430</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>400207</t>
+          <t>556012</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>612419</t>
+          <t>601766</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>850248</t>
+          <t>944924</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>704484</t>
+          <t>908227</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>911669</t>
+          <t>980916</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>70,4%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>471596</t>
+          <t>564367</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>471596</t>
+          <t>564367</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>471596</t>
+          <t>564367</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>840010</t>
+          <t>828983</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>840010</t>
+          <t>828983</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>840010</t>
+          <t>828983</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1311606</t>
+          <t>1393351</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1311606</t>
+          <t>1393351</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1311606</t>
+          <t>1393351</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>76591</t>
+          <t>79051</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54318</t>
+          <t>60159</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>102764</t>
+          <t>104705</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>234781</t>
+          <t>264726</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>212372</t>
+          <t>239390</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>261528</t>
+          <t>291491</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>311372</t>
+          <t>343777</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>276052</t>
+          <t>308145</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>344509</t>
+          <t>377485</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>163916</t>
+          <t>158177</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>137743</t>
+          <t>132523</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>186189</t>
+          <t>177069</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>525151</t>
+          <t>577952</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>498404</t>
+          <t>551187</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>547560</t>
+          <t>603288</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>689067</t>
+          <t>736129</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>655930</t>
+          <t>702421</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>724387</t>
+          <t>771761</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>71,47%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>759932</t>
+          <t>842678</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>759932</t>
+          <t>842678</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>759932</t>
+          <t>842678</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000439</t>
+          <t>1079906</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000439</t>
+          <t>1079906</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000439</t>
+          <t>1079906</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1248175</t>
+          <t>1111436</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1055369</t>
+          <t>1048469</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1752406</t>
+          <t>1169297</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1171119</t>
+          <t>1008861</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>986957</t>
+          <t>958923</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1615765</t>
+          <t>1058299</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2419294</t>
+          <t>2120298</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2112910</t>
+          <t>2043966</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2986882</t>
+          <t>2203640</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2120688</t>
+          <t>2323507</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1616457</t>
+          <t>2265646</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2313494</t>
+          <t>2386474</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2398034</t>
+          <t>2617035</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1953388</t>
+          <t>2567597</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2582196</t>
+          <t>2666973</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4518722</t>
+          <t>4940541</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3951134</t>
+          <t>4857199</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4825106</t>
+          <t>5016873</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>71,05%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3368863</t>
+          <t>3434943</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3368863</t>
+          <t>3434943</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3368863</t>
+          <t>3434943</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3569153</t>
+          <t>3625896</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3569153</t>
+          <t>3625896</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3569153</t>
+          <t>3625896</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6938016</t>
+          <t>7060839</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6938016</t>
+          <t>7060839</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6938016</t>
+          <t>7060839</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
